--- a/driver_forms/001_online_taxi_booking_form--driver_forms.xlsx
+++ b/driver_forms/001_online_taxi_booking_form--driver_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,12 +707,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'free',_'label':_'free'}</t>
+          <t>free</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Free', 'label': 'Free'}</t>
+          <t>Free</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'paid',_'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Paid', 'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'one-way',_'label':_'one_way'}</t>
+          <t>one_way</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'One-way', 'label': 'One way'}</t>
+          <t>One way</t>
         </is>
       </c>
     </row>
@@ -791,29 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'round-trip',_'label':_'round_trip'}</t>
+          <t>round_trip</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Round-trip', 'label': 'Round trip'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>select_trip_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>{'value':_'oneway',_'label':_'one_way'}</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>{'value': 'Oneway', 'label': 'One way'}</t>
+          <t>Round trip</t>
         </is>
       </c>
     </row>
